--- a/files/九龙-将军澳-Seasons Place.xlsx
+++ b/files/九龙-将军澳-Seasons Place.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -21125,7 +20997,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -30577,6180 +30449,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Seasons Place - 3A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>350 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>346 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>66/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$930万
-$20,983/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$886万
-$17,897/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$901万
-$19,887/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$889万
-$20,334/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$615万
-$19,052/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$727万
-$22,021/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>65/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$736万
-$16,605/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$759万
-$15,333/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$681万
-$15,035/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$670万
-$15,330/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$494万
-$15,282/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$494万
-$15,282/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$534万
-$16,194/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>63/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$731万
-$16,494/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$757万
-$15,301/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$680万
-$15,007/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$668万
-$15,293/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$493万
-$15,251/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$493万
-$15,251/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$540万
-$16,361/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$739万
-$16,688/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$756万
-$15,269/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$679万
-$14,985/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$667万
-$15,261/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$503万
-$15,563/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$503万
-$15,563/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$535万
-$16,200/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$695万
-$15,688/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$754万
-$15,236/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$678万
-$14,960/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$666万
-$15,231/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$502万
-$15,529/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$490万
-$15,186/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$531万
-$16,091/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$709万
-$16,011/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$750万
-$15,143/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$692万
-$15,278/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$664万
-$15,199/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$489万
-$15,152/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$489万
-$15,152/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$530万
-$16,061/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$704万
-$15,889/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$748万
-$15,111/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$676万
-$14,918/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$678万
-$15,510/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$488万
-$15,121/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$488万
-$15,121/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$529万
-$16,024/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$707万
-$15,953/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$747万
-$15,089/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$675万
-$14,894/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$662万
-$15,142/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$488万
-$15,099/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$488万
-$15,099/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$528万
-$16,003/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$704万
-$15,887/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$761万
-$15,368/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$673万
-$14,859/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$674万
-$15,423/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$486万
-$15,034/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$486万
-$15,034/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$526万
-$15,933/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$687万
-$15,499/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$759万
-$15,335/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$687万
-$15,174/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$658万
-$15,048/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$485万
-$15,003/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$496万
-$15,344/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$525万
-$15,900/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$686万
-$15,476/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$783万
-$15,812/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$686万
-$15,141/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$656万
-$15,016/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$484万
-$14,972/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$484万
-$14,972/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$524万
-$15,870/呎
-(24年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$684万
-$15,445/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$739万
-$14,931/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$684万
-$15,110/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$655万
-$14,984/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$510万
-$15,789/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$483万
-$14,941/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$522万
-$15,833/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$683万
-$15,413/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$738万
-$14,901/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$683万
-$15,079/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$653万
-$14,952/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$482万
-$14,910/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$509万
-$15,755/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$521万
-$15,800/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$681万
-$15,379/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$736万
-$14,869/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$682万
-$15,044/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$719万
-$16,449/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$508万
-$15,721/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$520万
-$16,099/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$520万
-$15,767/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$695万
-$15,695/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$734万
-$14,836/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$680万
-$15,015/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$688万
-$15,737/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$507万
-$15,690/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$507万
-$15,690/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$508万
-$15,388/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$679万
-$15,323/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$733万
-$14,816/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$664万
-$14,658/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$650万
-$14,867/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$479万
-$14,824/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$479万
-$14,824/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$507万
-$15,361/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$691万
-$15,605/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$747万
-$15,087/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$676万
-$14,927/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$647万
-$14,803/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$477万
-$14,762/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$477万
-$14,755/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$505万
-$15,297/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$675万
-$15,228/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$729万
-$14,721/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$660万
-$14,567/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$646万
-$14,776/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$476万
-$14,731/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$486万
-$15,056/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$504万
-$15,264/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$688万
-$15,542/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$727万
-$14,693/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$658万
-$14,536/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$649万
-$14,854/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$475万
-$14,700/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$475万
-$14,693/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$514万
-$15,582/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$687万
-$15,510/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$737万
-$14,881/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$672万
-$14,841/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$648万
-$14,824/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$480万
-$14,861/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$491万
-$15,189/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$502万
-$15,203/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$671万
-$15,144/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$741万
-$14,966/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$654万
-$14,428/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$642万
-$14,684/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$484万
-$14,975/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$483万
-$14,966/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$501万
-$15,176/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$670万
-$15,113/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$723万
-$14,606/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$652万
-$14,400/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$640万
-$14,657/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$499万
-$15,446/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$472万
-$14,607/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$511万
-$15,488/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$683万
-$15,424/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$722万
-$14,576/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$651万
-$14,371/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$639万
-$14,627/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$498万
-$15,412/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$498万
-$15,406/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$499万
-$15,112/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$667万
-$15,052/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$720万
-$14,545/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$650万
-$14,342/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$703万
-$16,094/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$470万
-$14,554/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$470万
-$14,548/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$498万
-$15,085/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$666万
-$15,029/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$719万
-$14,525/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$649万
-$14,322/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$673万
-$15,405/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$469万
-$14,533/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$496万
-$15,350/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$491万
-$14,867/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$663万
-$14,971/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$727万
-$14,683/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$646万
-$14,263/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$634万
-$14,517/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$484万
-$15,000/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$484万
-$14,991/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$489万
-$14,806/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$662万
-$14,939/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$715万
-$14,438/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$645万
-$14,236/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$638万
-$14,604/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$467万
-$14,446/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$466万
-$14,440/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$488万
-$14,779/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$660万
-$14,910/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$713万
-$14,410/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$644万
-$14,208/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$673万
-$15,403/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$466万
-$14,418/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$465万
-$14,409/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$514万
-$15,585/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$659万
-$14,883/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$752万
-$15,196/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$679万
-$14,985/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$672万
-$15,371/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$465万
-$14,390/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$464万
-$14,381/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$486万
-$14,718/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$658万
-$14,849/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$710万
-$14,352/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$641万
-$14,152/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$629万
-$14,400/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$464万
-$14,359/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$464万
-$14,353/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$485万
-$14,691/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$672万
-$15,165/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$709万
-$14,323/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$640万
-$14,124/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$628万
-$14,375/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$463万
-$14,331/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$489万
-$15,139/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$484万
-$14,661/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$693万
-$15,639/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$718万
-$14,507/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$653万
-$14,415/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$641万
-$14,670/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$468万
-$14,486/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$478万
-$14,808/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$483万
-$14,630/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$654万
-$14,770/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$797万
-$16,099/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$637万
-$14,066/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$661万
-$15,130/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$461万
-$14,276/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$487万
-$15,077/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$493万
-$14,933/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$653万
-$14,749/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$705万
-$14,244/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$636万
-$14,046/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$625万
-$14,295/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$460万
-$14,254/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$460万
-$14,245/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$481万
-$14,579/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$651万
-$14,688/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$702万
-$14,188/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$634万
-$13,989/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$620万
-$14,188/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$458万
-$14,195/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$458万
-$14,189/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$479万
-$14,521/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$649万
-$14,659/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$701万
-$14,160/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$632万
-$13,962/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$690万
-$15,789/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$468万
-$14,489/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$483万
-$14,966/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H41" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$478万
-$14,491/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$663万
-$14,962/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$700万
-$14,131/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$646万
-$14,249/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$653万
-$14,934/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$457万
-$14,139/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$456万
-$14,133/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H42" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$488万
-$14,791/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$647万
-$14,600/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$708万
-$14,313/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$630万
-$13,905/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$657万
-$15,032/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$456万
-$14,111/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$456万
-$14,105/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H43" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$476万
-$14,436/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$660万
-$14,903/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$697万
-$14,075/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$643万
-$14,194/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$620万
-$14,197/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$465万
-$14,402/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$465万
-$14,393/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$475万
-$14,406/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$644万
-$14,542/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$710万
-$14,352/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$627万
-$13,837/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$614万
-$14,048/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$464万
-$14,375/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$454万
-$14,050/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$474万
-$14,379/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$643万
-$14,519/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$693万
-$14,002/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$626万
-$13,810/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$613万
-$14,018/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$463万
-$14,347/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$463万
-$14,337/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$474万
-$14,348/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$657万
-$14,835/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$692万
-$13,990/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$660万
-$14,578/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$612万
-$14,005/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$453万
-$14,012/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$452万
-$14,006/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$473万
-$14,333/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$676万
-$15,269/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$705万
-$14,251/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$658万
-$14,521/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$624万
-$14,268/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$461万
-$14,272/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$461万
-$14,266/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H48" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$482万
-$14,603/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$639万
-$14,420/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$688万
-$13,907/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$698万
-$15,419/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$608万
-$13,922/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$460万
-$14,245/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$450万
-$13,923/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$470万
-$14,248/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$637万
-$14,388/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$687万
-$13,881/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$620万
-$13,684/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$607万
-$13,895/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$449万
-$13,913/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$449万
-$13,907/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$469万
-$14,212/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$636万
-$14,363/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$722万
-$14,582/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$654万
-$14,433/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$640万
-$14,654/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$449万
-$13,898/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$459万
-$14,207/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$468万
-$14,185/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="65" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$635万
-$14,334/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$682万
-$13,768/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$617万
-$13,629/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$605万
-$13,838/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$474万
-$14,672/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$458万
-$14,192/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="H52" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$467万
-$14,158/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="65" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$634万
-$14,305/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$680万
-$13,741/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$630万
-$13,914/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$617万
-$14,124/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$473万
-$14,656/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$473万
-$14,647/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H53" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$466万
-$14,127/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="65" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$632万
-$14,275/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$679万
-$13,713/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$615万
-$13,576/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$602万
-$13,783/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$458万
-$14,164/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$447万
-$13,845/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H54" s="16" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$492万
-$14,903/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="65" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>A | 408呎 (2房)
-$772万
-$18,922/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$678万
-$13,701/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>C | 415呎 (2房)
-$807万
-$19,437/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>D | 399呎 (2房)
-$681万
-$17,063/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>E | 286呎 (1房)
-$523万
-$18,294/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-$512万
-$17,975/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H55" s="16" t="inlineStr">
-        <is>
-          <t>G | 290呎 (1房)
-$561万
-$19,341/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Seasons Place - 3B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>300 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>297 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>66/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,261万
-$18,959/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$853万
-$19,007/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$731万
-$21,697/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$871万
-$19,753/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$587万
-$18,243/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$964万
-$21,577/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>65/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,186万
-$17,829/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$723万
-$16,109/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$548万
-$16,249/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$677万
-$15,358/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$510万
-$15,832/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$742万
-$16,602/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>63/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,114万
-$16,758/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$719万
-$16,004/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$529万
-$15,691/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$676万
-$15,324/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$497万
-$15,447/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$725万
-$16,219/呎
-(25年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,143万
-$17,182/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$717万
-$15,969/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$543万
-$16,110/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$713万
-$16,163/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$496万
-$15,416/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$706万
-$15,792/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,090万
-$16,391/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$716万
-$15,935/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$542万
-$16,071/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$673万
-$15,261/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$495万
-$15,382/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$701万
-$15,689/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,072万
-$16,117/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$698万
-$15,550/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$540万
-$16,039/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$672万
-$15,229/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$522万
-$16,220/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$700万
-$15,658/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,110万
-$16,695/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$716万
-$15,958/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$539万
-$16,003/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$670万
-$15,197/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$493万
-$15,317/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$733万
-$16,396/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,068万
-$16,057/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$711万
-$15,844/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$536万
-$15,890/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$669万
-$15,172/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$492万
-$15,295/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$732万
-$16,371/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,063万
-$15,991/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$708万
-$15,777/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$536万
-$15,914/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$666万
-$15,109/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$490万
-$15,230/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$729万
-$16,300/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,077万
-$16,195/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$703万
-$15,657/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$535万
-$15,881/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$665万
-$15,077/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$489万
-$15,199/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$727万
-$16,268/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,099万
-$16,529/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$690万
-$15,370/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$534万
-$15,846/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$664万
-$15,045/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$488万
-$15,168/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$726万
-$16,233/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,072万
-$16,128/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$689万
-$15,336/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$533万
-$15,813/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$662万
-$15,016/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$487万
-$15,134/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$706万
-$15,794/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,078万
-$16,217/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$703万
-$15,655/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$532万
-$15,780/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$661万
-$14,984/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$486万
-$15,102/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$689万
-$15,412/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,112万
-$16,723/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$686万
-$15,272/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$528万
-$15,662/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$659万
-$14,950/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$485万
-$15,071/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$703万
-$15,727/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,050万
-$15,791/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$684万
-$15,241/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 337呎 (1房)
-$515万
-$15,279/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$658万
-$14,921/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$484万
-$15,040/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$686万
-$15,347/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,088万
-$16,365/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$699万
-$15,563/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$530万
-$15,689/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$657万
-$14,898/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$511万
-$15,866/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$700万
-$15,671/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,060万
-$15,935/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$680万
-$15,154/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$528万
-$15,621/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$654万
-$14,834/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$509万
-$15,804/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$682万
-$15,257/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,082万
-$16,263/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$694万
-$15,465/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$524万
-$15,503/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$653万
-$14,803/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$480万
-$14,919/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$681万
-$15,228/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,055万
-$15,869/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$678万
-$15,091/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$526万
-$15,559/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$656万
-$14,884/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$480万
-$14,894/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$718万
-$16,060/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,077万
-$16,197/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$676万
-$15,065/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$525万
-$15,530/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$655万
-$14,855/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$479万
-$14,863/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$716万
-$16,029/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,111万
-$16,704/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$675万
-$15,040/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$524万
-$15,500/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$649万
-$14,714/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$505万
-$15,674/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$677万
-$15,143/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,034万
-$15,543/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$674万
-$15,011/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$523万
-$15,464/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$648万
-$14,685/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$477万
-$14,804/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$675万
-$15,110/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,090万
-$16,392/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$688万
-$15,318/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$519万
-$15,352/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$646万
-$14,655/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$486万
-$15,106/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$689万
-$15,423/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,053万
-$15,833/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$671万
-$14,949/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$518万
-$15,320/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$645万
-$14,628/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$475万
-$14,742/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$673万
-$15,051/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,051万
-$15,809/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$663万
-$14,757/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$514万
-$15,210/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$659万
-$14,939/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$501万
-$15,556/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$672万
-$15,029/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,024万
-$15,395/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$660万
-$14,699/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$512万
-$15,154/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$642万
-$14,546/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$472万
-$14,665/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$669万
-$14,971/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,022万
-$15,365/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$679万
-$15,122/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$502万
-$14,867/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$645万
-$14,635/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$498万
-$15,466/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$683万
-$15,280/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,078万
-$16,205/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$678万
-$15,094/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$530万
-$15,683/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$644万
-$14,605/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$470万
-$14,602/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$682万
-$15,248/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,018万
-$15,305/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$676万
-$15,062/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$500万
-$14,808/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$643万
-$14,576/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$469万
-$14,578/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$680万
-$15,219/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,039万
-$15,620/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$655万
-$14,581/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$500万
-$14,781/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$672万
-$15,249/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$479万
-$14,879/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$674万
-$15,067/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,014万
-$15,242/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$653万
-$14,552/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$527万
-$15,589/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$635万
-$14,401/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$467万
-$14,516/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$672万
-$15,040/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,100万
-$16,541/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$652万
-$14,523/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$498万
-$14,719/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$634万
-$14,374/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$467万
-$14,491/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$656万
-$14,676/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,010万
-$15,183/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$651万
-$14,494/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$496万
-$14,689/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$633万
-$14,345/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$466万
-$14,460/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$655万
-$14,644/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,008万
-$15,161/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$650万
-$14,472/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$496万
-$14,669/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$632万
-$14,324/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$465万
-$14,438/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$654万
-$14,624/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,004万
-$15,098/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$647万
-$14,416/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$522万
-$15,441/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$644万
-$14,592/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$474万
-$14,705/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$651万
-$14,566/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,002万
-$15,069/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$721万
-$16,058/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$493万
-$14,583/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$628万
-$14,238/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$462万
-$14,351/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$664万
-$14,866/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,000万
-$15,039/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$681万
-$15,174/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$492万
-$14,553/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$627万
-$14,209/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$461万
-$14,323/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$646万
-$14,456/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$998万
-$15,009/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$649万
-$14,452/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$491万
-$14,524/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$666万
-$15,113/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$460万
-$14,298/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$650万
-$14,553/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$996万
-$14,979/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$648万
-$14,423/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$490万
-$14,494/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$630万
-$14,274/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$470万
-$14,590/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$649万
-$14,521/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$994万
-$14,949/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$641万
-$14,272/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$500万
-$14,793/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$637万
-$14,447/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$469万
-$14,562/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$642万
-$14,369/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$992万
-$14,919/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$654万
-$14,568/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$488万
-$14,435/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$636万
-$14,417/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$458万
-$14,211/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$656万
-$14,669/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$991万
-$14,905/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$653万
-$14,552/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$515万
-$15,240/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$621万
-$14,084/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$483万
-$15,003/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$655万
-$14,653/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$987万
-$14,844/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$636万
-$14,174/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$486万
-$14,364/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$618万
-$14,025/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$481万
-$14,941/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$652万
-$14,595/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$985万
-$14,815/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$635万
-$14,145/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$485万
-$14,337/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$617万
-$13,998/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$481万
-$14,925/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$637万
-$14,242/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$979万
-$14,726/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$648万
-$14,437/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$511万
-$15,118/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$616万
-$13,968/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$464万
-$14,425/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$635万
-$14,213/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$977万
-$14,696/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$633万
-$14,089/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$510万
-$15,092/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$615万
-$13,941/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$480万
-$14,894/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$634万
-$14,186/呎
-(24年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="65" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$975万
-$14,668/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$631万
-$14,060/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$509万
-$15,059/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$614万
-$13,916/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$453万
-$14,075/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$669万
-$14,960/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="65" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$996万
-$14,970/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$630万
-$14,031/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$489万
-$14,464/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$626万
-$14,204/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$478万
-$14,857/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$632万
-$14,128/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="65" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>A | 665呎 (3房)
-$1,027万
-$15,439/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$629万
-$14,002/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$507万
-$15,000/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>D | 441呎 (2房)
-$611万
-$13,857/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$463万
-$14,366/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>F | 447呎 (2房)
-$630万
-$14,098/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="65" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>A | 627呎 (3房)
-$1,078万
-$17,188/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>B | 411呎 (2房)
-$710万
-$17,273/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>C | 300呎 (1房)
-$545万
-$18,153/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>D | 405呎 (2房)
-$715万
-$17,662/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>E | 282呎 (1房)
-$568万
-$20,125/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>F | 409呎 (2房)
-$742万
-$18,142/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-将军澳-Seasons Place.xlsx
+++ b/files/九龙-将军澳-Seasons Place.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,97 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +144,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +219,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -30449,4 +30621,6180 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$930万
+$20,983/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$886万
+$17,897/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$901万
+$19,887/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$889万
+$20,334/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$615万
+$19,052/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$727万
+$22,021/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$736万
+$16,605/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$759万
+$15,333/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$681万
+$15,035/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$670万
+$15,330/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$494万
+$15,282/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$494万
+$15,282/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$534万
+$16,194/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$731万
+$16,494/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$757万
+$15,301/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$680万
+$15,007/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$668万
+$15,293/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$493万
+$15,251/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$493万
+$15,251/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$540万
+$16,361/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$739万
+$16,688/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$756万
+$15,269/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$679万
+$14,985/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$667万
+$15,261/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$503万
+$15,563/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$503万
+$15,563/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$535万
+$16,200/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$695万
+$15,688/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$754万
+$15,236/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$678万
+$14,960/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$666万
+$15,231/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$502万
+$15,529/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$490万
+$15,186/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$531万
+$16,091/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$709万
+$16,011/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$750万
+$15,143/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$692万
+$15,278/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$664万
+$15,199/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$489万
+$15,152/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$489万
+$15,152/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$530万
+$16,061/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$704万
+$15,889/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$748万
+$15,111/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$676万
+$14,918/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$678万
+$15,510/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$488万
+$15,121/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$488万
+$15,121/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$529万
+$16,024/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$707万
+$15,953/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$747万
+$15,089/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$675万
+$14,894/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$662万
+$15,142/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$488万
+$15,099/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$488万
+$15,099/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$528万
+$16,003/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$704万
+$15,887/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$761万
+$15,368/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$673万
+$14,859/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$674万
+$15,423/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$486万
+$15,034/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$486万
+$15,034/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$526万
+$15,933/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$687万
+$15,499/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$759万
+$15,335/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$687万
+$15,174/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$658万
+$15,048/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$485万
+$15,003/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$496万
+$15,344/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$525万
+$15,900/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$686万
+$15,476/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$783万
+$15,812/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$686万
+$15,141/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$656万
+$15,016/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$484万
+$14,972/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$484万
+$14,972/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$524万
+$15,870/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$684万
+$15,445/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$739万
+$14,931/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$684万
+$15,110/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$655万
+$14,984/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$510万
+$15,789/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$483万
+$14,941/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$522万
+$15,833/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$683万
+$15,413/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$738万
+$14,901/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$683万
+$15,079/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$653万
+$14,952/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$482万
+$14,910/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$509万
+$15,755/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$521万
+$15,800/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$681万
+$15,379/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$736万
+$14,869/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$682万
+$15,044/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$719万
+$16,449/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$508万
+$15,721/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$520万
+$16,099/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$520万
+$15,767/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$695万
+$15,695/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$734万
+$14,836/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$680万
+$15,015/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$688万
+$15,737/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$507万
+$15,690/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$507万
+$15,690/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$508万
+$15,388/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$679万
+$15,323/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$733万
+$14,816/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$664万
+$14,658/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$650万
+$14,867/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$479万
+$14,824/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$479万
+$14,824/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$507万
+$15,361/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$691万
+$15,605/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$747万
+$15,087/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$676万
+$14,927/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$647万
+$14,803/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$477万
+$14,762/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$477万
+$14,755/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$505万
+$15,297/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$675万
+$15,228/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$729万
+$14,721/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$660万
+$14,567/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$646万
+$14,776/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$476万
+$14,731/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$486万
+$15,056/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$504万
+$15,264/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$688万
+$15,542/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$727万
+$14,693/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$658万
+$14,536/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$649万
+$14,854/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$475万
+$14,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$475万
+$14,693/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$514万
+$15,582/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$687万
+$15,510/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$737万
+$14,881/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$672万
+$14,841/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$648万
+$14,824/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$480万
+$14,861/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$491万
+$15,189/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$502万
+$15,203/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$671万
+$15,144/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$741万
+$14,966/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$654万
+$14,428/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$642万
+$14,684/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$484万
+$14,975/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$483万
+$14,966/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$501万
+$15,176/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$670万
+$15,113/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$723万
+$14,606/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$652万
+$14,400/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$640万
+$14,657/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$499万
+$15,446/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$472万
+$14,607/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$511万
+$15,488/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$683万
+$15,424/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$722万
+$14,576/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$651万
+$14,371/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$639万
+$14,627/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$498万
+$15,412/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$498万
+$15,406/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$499万
+$15,112/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$667万
+$15,052/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$720万
+$14,545/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$650万
+$14,342/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$703万
+$16,094/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$470万
+$14,554/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$470万
+$14,548/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$498万
+$15,085/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$666万
+$15,029/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$719万
+$14,525/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$649万
+$14,322/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$673万
+$15,405/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$469万
+$14,533/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$496万
+$15,350/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$491万
+$14,867/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$663万
+$14,971/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$727万
+$14,683/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$646万
+$14,263/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$634万
+$14,517/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$484万
+$15,000/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$484万
+$14,991/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$489万
+$14,806/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$662万
+$14,939/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$715万
+$14,438/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$645万
+$14,236/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$638万
+$14,604/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$467万
+$14,446/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$466万
+$14,440/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$488万
+$14,779/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$660万
+$14,910/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$713万
+$14,410/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$644万
+$14,208/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$673万
+$15,403/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$466万
+$14,418/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$465万
+$14,409/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$514万
+$15,585/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$659万
+$14,883/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$752万
+$15,196/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$679万
+$14,985/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$672万
+$15,371/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$465万
+$14,390/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$464万
+$14,381/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$486万
+$14,718/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$658万
+$14,849/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$710万
+$14,352/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$641万
+$14,152/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$629万
+$14,400/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$464万
+$14,359/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$464万
+$14,353/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$485万
+$14,691/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$672万
+$15,165/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$709万
+$14,323/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$640万
+$14,124/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$628万
+$14,375/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$463万
+$14,331/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$489万
+$15,139/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$484万
+$14,661/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$693万
+$15,639/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$718万
+$14,507/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$653万
+$14,415/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$641万
+$14,670/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$468万
+$14,486/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$478万
+$14,808/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$483万
+$14,630/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$654万
+$14,770/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$797万
+$16,099/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$637万
+$14,066/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$661万
+$15,130/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$461万
+$14,276/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$487万
+$15,077/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$493万
+$14,933/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$653万
+$14,749/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$705万
+$14,244/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$636万
+$14,046/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$625万
+$14,295/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$460万
+$14,254/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$460万
+$14,245/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$481万
+$14,579/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$651万
+$14,688/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$702万
+$14,188/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$634万
+$13,989/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$620万
+$14,188/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$458万
+$14,195/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$458万
+$14,189/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$479万
+$14,521/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$649万
+$14,659/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$701万
+$14,160/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$632万
+$13,962/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$690万
+$15,789/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$468万
+$14,489/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$483万
+$14,966/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$478万
+$14,491/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$663万
+$14,962/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$700万
+$14,131/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$646万
+$14,249/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$653万
+$14,934/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$457万
+$14,139/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$456万
+$14,133/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$488万
+$14,791/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$647万
+$14,600/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$708万
+$14,313/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$630万
+$13,905/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$657万
+$15,032/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$456万
+$14,111/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$456万
+$14,105/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$476万
+$14,436/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$660万
+$14,903/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$697万
+$14,075/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$643万
+$14,194/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$620万
+$14,197/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$465万
+$14,402/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$465万
+$14,393/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$475万
+$14,406/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$644万
+$14,542/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$710万
+$14,352/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$627万
+$13,837/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$614万
+$14,048/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$464万
+$14,375/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$454万
+$14,050/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$474万
+$14,379/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$643万
+$14,519/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$693万
+$14,002/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$626万
+$13,810/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$613万
+$14,018/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$463万
+$14,347/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$463万
+$14,337/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$474万
+$14,348/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$657万
+$14,835/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$692万
+$13,990/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$660万
+$14,578/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$612万
+$14,005/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$453万
+$14,012/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$452万
+$14,006/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$473万
+$14,333/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$676万
+$15,269/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$705万
+$14,251/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$658万
+$14,521/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$624万
+$14,268/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$461万
+$14,272/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$461万
+$14,266/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$482万
+$14,603/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$639万
+$14,420/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$688万
+$13,907/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$698万
+$15,419/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$608万
+$13,922/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$460万
+$14,245/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$450万
+$13,923/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$470万
+$14,248/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$637万
+$14,388/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$687万
+$13,881/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$620万
+$13,684/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$607万
+$13,895/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$449万
+$13,913/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$449万
+$13,907/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$469万
+$14,212/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$636万
+$14,363/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$722万
+$14,582/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$654万
+$14,433/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$640万
+$14,654/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$449万
+$13,898/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$459万
+$14,207/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H50" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$468万
+$14,185/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$635万
+$14,334/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$682万
+$13,768/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$617万
+$13,629/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$605万
+$13,838/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$474万
+$14,672/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$458万
+$14,192/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$467万
+$14,158/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$634万
+$14,305/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$680万
+$13,741/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$630万
+$13,914/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$617万
+$14,124/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$473万
+$14,656/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$473万
+$14,647/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$466万
+$14,127/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$632万
+$14,275/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$679万
+$13,713/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$615万
+$13,576/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$602万
+$13,783/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$458万
+$14,164/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$447万
+$13,845/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$492万
+$14,903/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>A | 408呎 (2房)
+$772万
+$18,922/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$678万
+$13,701/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>C | 415呎 (2房)
+$807万
+$19,437/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>D | 399呎 (2房)
+$681万
+$17,063/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>E | 286呎 (1房)
+$523万
+$18,294/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+$512万
+$17,975/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>G | 290呎 (1房)
+$561万
+$19,341/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1261万
+$18,959/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$853万
+$19,007/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$731万
+$21,697/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$871万
+$19,753/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$587万
+$18,243/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$964万
+$21,577/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1186万
+$17,829/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$723万
+$16,109/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$548万
+$16,249/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$677万
+$15,358/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$510万
+$15,832/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$742万
+$16,602/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1114万
+$16,758/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$719万
+$16,004/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$529万
+$15,691/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$676万
+$15,324/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$497万
+$15,447/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$725万
+$16,219/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1143万
+$17,182/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$717万
+$15,969/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$543万
+$16,110/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$713万
+$16,163/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$496万
+$15,416/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$706万
+$15,792/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1090万
+$16,391/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$716万
+$15,935/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$542万
+$16,071/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$673万
+$15,261/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$495万
+$15,382/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$701万
+$15,689/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1072万
+$16,117/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$698万
+$15,550/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$540万
+$16,039/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$672万
+$15,229/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$522万
+$16,220/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$700万
+$15,658/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1110万
+$16,695/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$716万
+$15,958/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$539万
+$16,003/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$670万
+$15,197/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$493万
+$15,317/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$733万
+$16,396/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1068万
+$16,057/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$711万
+$15,844/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$536万
+$15,890/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$669万
+$15,172/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$492万
+$15,295/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$732万
+$16,371/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1063万
+$15,991/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$708万
+$15,777/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$536万
+$15,914/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$666万
+$15,109/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$490万
+$15,230/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$729万
+$16,300/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1077万
+$16,195/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$703万
+$15,657/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$535万
+$15,881/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$665万
+$15,077/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$489万
+$15,199/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$727万
+$16,268/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1099万
+$16,529/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$690万
+$15,370/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$534万
+$15,846/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$664万
+$15,045/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$488万
+$15,168/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$726万
+$16,233/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1072万
+$16,128/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$689万
+$15,336/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$533万
+$15,813/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$662万
+$15,016/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$487万
+$15,134/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$706万
+$15,794/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1078万
+$16,217/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$703万
+$15,655/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$532万
+$15,780/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$661万
+$14,984/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$486万
+$15,102/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$689万
+$15,412/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1112万
+$16,723/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$686万
+$15,272/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$528万
+$15,662/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$659万
+$14,950/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$485万
+$15,071/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$703万
+$15,727/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1050万
+$15,791/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$684万
+$15,241/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 337呎 (1房)
+$515万
+$15,279/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$658万
+$14,921/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$484万
+$15,040/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$686万
+$15,347/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1088万
+$16,365/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$699万
+$15,563/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$530万
+$15,689/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$657万
+$14,898/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$511万
+$15,866/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$700万
+$15,671/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1060万
+$15,935/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$680万
+$15,154/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$528万
+$15,621/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$654万
+$14,834/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$509万
+$15,804/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$682万
+$15,257/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1082万
+$16,263/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$694万
+$15,465/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$524万
+$15,503/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$653万
+$14,803/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$480万
+$14,919/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$681万
+$15,228/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1055万
+$15,869/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$678万
+$15,091/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$526万
+$15,559/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$656万
+$14,884/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$480万
+$14,894/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$718万
+$16,060/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1077万
+$16,197/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$676万
+$15,065/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$525万
+$15,530/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$655万
+$14,855/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$479万
+$14,863/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$716万
+$16,029/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1111万
+$16,704/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$675万
+$15,040/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$524万
+$15,500/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$649万
+$14,714/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$505万
+$15,674/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$677万
+$15,143/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1034万
+$15,543/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$674万
+$15,011/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$523万
+$15,464/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$648万
+$14,685/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$477万
+$14,804/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$675万
+$15,110/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1090万
+$16,392/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$688万
+$15,318/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$519万
+$15,352/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$646万
+$14,655/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$486万
+$15,106/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$689万
+$15,423/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1053万
+$15,833/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$671万
+$14,949/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$518万
+$15,320/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$645万
+$14,628/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$475万
+$14,742/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$673万
+$15,051/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1051万
+$15,809/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$663万
+$14,757/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$514万
+$15,210/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$659万
+$14,939/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$501万
+$15,556/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$672万
+$15,029/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1024万
+$15,395/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$660万
+$14,699/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$512万
+$15,154/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$642万
+$14,546/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$472万
+$14,665/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$669万
+$14,971/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1022万
+$15,365/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$679万
+$15,122/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$502万
+$14,867/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$645万
+$14,635/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$498万
+$15,466/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$683万
+$15,280/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1078万
+$16,205/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$678万
+$15,094/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$530万
+$15,683/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$644万
+$14,605/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$470万
+$14,602/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$682万
+$15,248/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1018万
+$15,305/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$676万
+$15,062/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$500万
+$14,808/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$643万
+$14,576/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$469万
+$14,578/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$680万
+$15,219/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1039万
+$15,620/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$655万
+$14,581/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$500万
+$14,781/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$672万
+$15,249/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$479万
+$14,879/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$674万
+$15,067/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1014万
+$15,242/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$653万
+$14,552/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$527万
+$15,589/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$635万
+$14,401/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$467万
+$14,516/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$672万
+$15,040/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1100万
+$16,541/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$652万
+$14,523/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$498万
+$14,719/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$634万
+$14,374/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$467万
+$14,491/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$656万
+$14,676/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1010万
+$15,183/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$651万
+$14,494/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$496万
+$14,689/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$633万
+$14,345/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$466万
+$14,460/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$655万
+$14,644/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1008万
+$15,161/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$650万
+$14,472/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$496万
+$14,669/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$632万
+$14,324/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$465万
+$14,438/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$654万
+$14,624/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1004万
+$15,098/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$647万
+$14,416/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$522万
+$15,441/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$644万
+$14,592/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$474万
+$14,705/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$651万
+$14,566/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1002万
+$15,069/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$721万
+$16,058/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$493万
+$14,583/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$628万
+$14,238/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$462万
+$14,351/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$664万
+$14,866/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1000万
+$15,039/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$681万
+$15,174/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$492万
+$14,553/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$627万
+$14,209/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$461万
+$14,323/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$646万
+$14,456/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$998万
+$15,009/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$649万
+$14,452/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$491万
+$14,524/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$666万
+$15,113/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$460万
+$14,298/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$650万
+$14,553/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$996万
+$14,979/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$648万
+$14,423/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$490万
+$14,494/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$630万
+$14,274/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$470万
+$14,590/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$649万
+$14,521/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$994万
+$14,949/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$641万
+$14,272/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$500万
+$14,793/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$637万
+$14,447/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$469万
+$14,562/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$642万
+$14,369/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$992万
+$14,919/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$654万
+$14,568/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$488万
+$14,435/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$636万
+$14,417/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$458万
+$14,211/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$656万
+$14,669/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$991万
+$14,905/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$653万
+$14,552/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$515万
+$15,240/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$621万
+$14,084/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$483万
+$15,003/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$655万
+$14,653/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$987万
+$14,844/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$636万
+$14,174/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$486万
+$14,364/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$618万
+$14,025/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$481万
+$14,941/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$652万
+$14,595/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$985万
+$14,815/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$635万
+$14,145/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$485万
+$14,337/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$617万
+$13,998/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$481万
+$14,925/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$637万
+$14,242/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$979万
+$14,726/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$648万
+$14,437/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$511万
+$15,118/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$616万
+$13,968/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$464万
+$14,425/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$635万
+$14,213/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$977万
+$14,696/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$633万
+$14,089/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$510万
+$15,092/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$615万
+$13,941/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$480万
+$14,894/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$634万
+$14,186/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$975万
+$14,668/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$631万
+$14,060/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$509万
+$15,059/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$614万
+$13,916/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$453万
+$14,075/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$669万
+$14,960/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$996万
+$14,970/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$630万
+$14,031/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$489万
+$14,464/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$626万
+$14,204/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$478万
+$14,857/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$632万
+$14,128/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>A | 665呎 (3房)
+$1027万
+$15,439/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$629万
+$14,002/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$507万
+$15,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>D | 441呎 (2房)
+$611万
+$13,857/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$463万
+$14,366/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$630万
+$14,098/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>A | 627呎 (3房)
+$1078万
+$17,188/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>B | 411呎 (2房)
+$710万
+$17,273/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>C | 300呎 (1房)
+$545万
+$18,153/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>D | 405呎 (2房)
+$715万
+$17,662/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>E | 282呎 (1房)
+$568万
+$20,125/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>F | 409呎 (2房)
+$742万
+$18,142/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-将军澳-Seasons Place.xlsx
+++ b/files/九龙-将军澳-Seasons Place.xlsx
@@ -646,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
